--- a/action_cop/output_excels/18_Investor_Complaints.xlsx
+++ b/action_cop/output_excels/18_Investor_Complaints.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
